--- a/customer_service_forms/007_support_customer_feedback_survey--customer_service_forms.xlsx
+++ b/customer_service_forms/007_support_customer_feedback_survey--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,155 +515,155 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey</t>
+          <t>How would you rate your overall satisfaction with our customer support?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_1</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_1</t>
+          <t>What was the reason for your last interaction with our support team?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_2</t>
+          <t>issue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>What was the issue you had with our support team?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_5</t>
+          <t>effectiveness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>How would you rate the effectiveness of our support team in resolving your issue?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_4</t>
+          <t>likelihood_to_recommend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_4</t>
+          <t>How likely are you to recommend our company to a friend or colleague?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_3</t>
+          <t>resolution</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_3</t>
+          <t>What was the resolution or outcome of your issue?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_6</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_6</t>
+          <t>Would you like to provide additional comments or feedback about your experience?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_7</t>
+          <t>support_team</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_7</t>
+          <t>What was the issue with our support team that you experienced?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,23 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_8</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey8</t>
+          <t>How would you rate the communication from our support team?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_9</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey9</t>
+          <t>What improvements would you like to see us make to improve customer support?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey</t>
+          <t>other_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey</t>
+          <t>Any other comments or suggestions?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_10</t>
+          <t>open_ended</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey10</t>
+          <t>Additional comments or feedback?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_11</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey11</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey12</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey13</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_6</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey6</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey10</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_7</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey7</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey4</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_8</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey8</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_9</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey9</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey11</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey12</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>support_customer_feedback_survey5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,153 +827,476 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_1_choices</t>
+          <t>rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'positive',_'label':_'positive'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'positive', 'label': 'positive'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_1_choices</t>
+          <t>rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'neutral', 'label': 'neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_1_choices</t>
+          <t>rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'negative',_'label':_'negative'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'negative', 'label': 'negative'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_6_choices</t>
+          <t>issue_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'positive',_'label':_'positive'}</t>
+          <t>not_familiar_with_the_product</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'positive', 'label': 'positive'}</t>
+          <t>Not familiar with the product</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_6_choices</t>
+          <t>issue_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'negative',_'label':_'negative'}</t>
+          <t>not_helpful</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'negative', 'label': 'negative'}</t>
+          <t>Not helpful</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_6_choices</t>
+          <t>issue_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'neutral',_'label':_'neutral'}</t>
+          <t>not_responsive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'neutral', 'label': 'neutral'}</t>
+          <t>Not responsive</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_10_choices</t>
+          <t>issue_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'positive',_'label':_'positive'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'positive', 'label': 'positive'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_10_choices</t>
+          <t>effectiveness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'neutral',_'label':_'neutral'}</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'neutral', 'label': 'neutral'}</t>
+          <t>Very effective</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>support_customer_feedback_survey_10_choices</t>
+          <t>effectiveness_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'negative',_'label':_'negative'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'negative', 'label': 'negative'}</t>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>very_ineffective</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Very ineffective</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>very_likely</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Very likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>somewhat_likely</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Somewhat likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>somewhat_unlikely</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Somewhat unlikely</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>likelihood_to_recommend_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>very_unlikely</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Very unlikely</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>resolution_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>issue_was_resolved</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Issue was resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>resolution_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>issue_was_not_resolved</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Issue was not resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>resolution_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>i_was_not_sure</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>I was not sure</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>resolution_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>support_team_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>not_helpful</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not helpful</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>support_team_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>not_responsive</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Not responsive</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>support_team_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>not_familiar_with_the_product</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Not familiar with the product</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>support_team_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>very_good</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Very good</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>somewhat_good</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Somewhat good</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>somewhat_poor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Somewhat poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>communication_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>very_poor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
